--- a/Excel/SoulRingConfig.xlsx
+++ b/Excel/SoulRingConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -35,6 +40,24 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Sid</t>
+  </si>
+  <si>
+    <t>StartLevel</t>
+  </si>
+  <si>
+    <t>EndLevel</t>
+  </si>
+  <si>
+    <t>AttrIdList</t>
+  </si>
+  <si>
+    <t>AttrValueList</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -44,28 +67,70 @@
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>double[]</t>
+  </si>
+  <si>
     <t>十年魂环</t>
   </si>
   <si>
+    <t>1,2,3,1001,1007,27</t>
+  </si>
+  <si>
+    <t>5000,500,500,5,1,1</t>
+  </si>
+  <si>
     <t>百年魂环</t>
   </si>
   <si>
+    <t>1,2,3,1002,1008,28</t>
+  </si>
+  <si>
     <t>千年魂环</t>
   </si>
   <si>
+    <t>1,2,3,1003,1009,27</t>
+  </si>
+  <si>
     <t>万年魂环</t>
   </si>
   <si>
-    <t>十万年魂环</t>
-  </si>
-  <si>
-    <t>百万年魂环</t>
-  </si>
-  <si>
-    <t>千万年魂环</t>
+    <t>1,2,3,1007,2001,28</t>
+  </si>
+  <si>
+    <t>10000,1000,1000,5,1,1</t>
+  </si>
+  <si>
+    <t>十万魂环</t>
+  </si>
+  <si>
+    <t>1,2,3,1008,2002,27</t>
+  </si>
+  <si>
+    <t>百万魂环</t>
+  </si>
+  <si>
+    <t>1,2,3,1009,2003,28</t>
+  </si>
+  <si>
+    <t>千万魂环</t>
+  </si>
+  <si>
+    <t>1,2,3,22,24,27</t>
+  </si>
+  <si>
+    <t>15000,1500,1500,5,5,1</t>
   </si>
   <si>
     <t>亿年魂环</t>
+  </si>
+  <si>
+    <t>1,2,3,22,24,28</t>
+  </si>
+  <si>
+    <t>20000,2000,2000,5,5,1</t>
   </si>
 </sst>
 </file>
@@ -78,7 +143,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,16 +152,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF05073B"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -568,143 +652,151 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1024,137 +1116,620 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <dimension ref="A1:J70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
+    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
-    <col min="5" max="16366" width="9" style="2"/>
+    <col min="5" max="5" width="14.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.9416666666667" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.4166666666667" style="4" customWidth="1"/>
+    <col min="8" max="8" width="28.8166666666667" style="5" customWidth="1"/>
+    <col min="9" max="9" width="27.8833333333333" style="5" customWidth="1"/>
+    <col min="10" max="10" width="18.8166666666667" style="5" customWidth="1"/>
+    <col min="11" max="16367" width="9" style="3"/>
+    <col min="16368" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:4">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="E4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C6">
+      <c r="H4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>30</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="4">
+        <v>8001</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>30</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="4">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>30</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="4">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>30</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="4">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C10" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>30</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="4">
+        <v>8005</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C11" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>30</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C12" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>30</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="4">
+        <v>8007</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C13" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C12">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" ht="27" customHeight="1" spans="3:4">
-      <c r="C13">
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="2">
         <v>8</v>
       </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="3:4">
-      <c r="C14"/>
-      <c r="D14"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="3:4">
-      <c r="C15"/>
-      <c r="D15"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="3:4">
-      <c r="C16"/>
-      <c r="D16"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="3:4">
-      <c r="C17"/>
-      <c r="D17"/>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>30</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="4">
+        <v>8008</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:10">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:10">
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:10">
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:10">
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:10">
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:10">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:10">
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:10">
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:10">
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:10">
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:10">
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" customHeight="1" spans="3:10">
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:10">
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:10">
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:10">
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:10">
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" customHeight="1" spans="8:9">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" customHeight="1" spans="8:9">
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" customHeight="1" spans="8:9">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" customHeight="1" spans="8:9">
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" customHeight="1" spans="8:9">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" customHeight="1" spans="8:9">
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" customHeight="1" spans="8:9">
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" customHeight="1" spans="8:9">
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" customHeight="1" spans="8:9">
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" customHeight="1" spans="8:9">
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="8:9">
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" customHeight="1" spans="8:9">
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" customHeight="1" spans="8:9">
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" customHeight="1" spans="8:9">
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="8:9">
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="8:9">
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+    </row>
+    <row r="50" customHeight="1" spans="8:9">
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" customHeight="1" spans="8:9">
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="8:9">
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" customHeight="1" spans="8:9">
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" customHeight="1" spans="8:9">
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" customHeight="1" spans="8:9">
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" customHeight="1" spans="8:9">
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" customHeight="1" spans="8:9">
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" customHeight="1" spans="8:9">
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" customHeight="1" spans="8:9">
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" customHeight="1" spans="8:9">
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" customHeight="1" spans="8:9">
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" customHeight="1" spans="8:9">
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+    </row>
+    <row r="63" customHeight="1" spans="8:9">
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+    </row>
+    <row r="64" customHeight="1" spans="8:9">
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+    </row>
+    <row r="65" customHeight="1" spans="8:9">
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+    </row>
+    <row r="66" customHeight="1" spans="8:9">
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+    </row>
+    <row r="67" customHeight="1" spans="8:9">
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" customHeight="1" spans="8:9">
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" customHeight="1" spans="8:9">
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" customHeight="1" spans="8:9">
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SoulRingConfig.xlsx
+++ b/Excel/SoulRingConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -43,16 +43,25 @@
     <t>Sid</t>
   </si>
   <si>
-    <t>StartLevel</t>
-  </si>
-  <si>
-    <t>EndLevel</t>
-  </si>
-  <si>
-    <t>AttrIdList</t>
-  </si>
-  <si>
-    <t>AttrValueList</t>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>RequireList</t>
+  </si>
+  <si>
+    <t>SpeIdList</t>
+  </si>
+  <si>
+    <t>SpeVueList</t>
+  </si>
+  <si>
+    <t>SpeRequireList</t>
   </si>
   <si>
     <t>ItemId</t>
@@ -82,18 +91,36 @@
     <t>5000,500,500,5,1,1</t>
   </si>
   <si>
+    <t>0,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>百年魂环</t>
   </si>
   <si>
     <t>1,2,3,1002,1008,28</t>
   </si>
   <si>
+    <t>10002</t>
+  </si>
+  <si>
     <t>千年魂环</t>
   </si>
   <si>
     <t>1,2,3,1003,1009,27</t>
   </si>
   <si>
+    <t>10003</t>
+  </si>
+  <si>
     <t>万年魂环</t>
   </si>
   <si>
@@ -103,18 +130,27 @@
     <t>10000,1000,1000,5,1,1</t>
   </si>
   <si>
+    <t>10007</t>
+  </si>
+  <si>
     <t>十万魂环</t>
   </si>
   <si>
     <t>1,2,3,1008,2002,27</t>
   </si>
   <si>
+    <t>10008</t>
+  </si>
+  <si>
     <t>百万魂环</t>
   </si>
   <si>
     <t>1,2,3,1009,2003,28</t>
   </si>
   <si>
+    <t>10009</t>
+  </si>
+  <si>
     <t>千万魂环</t>
   </si>
   <si>
@@ -124,6 +160,9 @@
     <t>15000,1500,1500,5,5,1</t>
   </si>
   <si>
+    <t>10027</t>
+  </si>
+  <si>
     <t>亿年魂环</t>
   </si>
   <si>
@@ -131,6 +170,9 @@
   </si>
   <si>
     <t>20000,2000,2000,5,5,1</t>
+  </si>
+  <si>
+    <t>10028</t>
   </si>
 </sst>
 </file>
@@ -143,7 +185,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +206,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,8 +226,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF05073B"/>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -652,151 +701,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1116,620 +1170,750 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.9416666666667" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.4166666666667" style="4" customWidth="1"/>
-    <col min="8" max="8" width="28.8166666666667" style="5" customWidth="1"/>
-    <col min="9" max="9" width="27.8833333333333" style="5" customWidth="1"/>
-    <col min="10" max="10" width="18.8166666666667" style="5" customWidth="1"/>
-    <col min="11" max="16367" width="9" style="3"/>
-    <col min="16368" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="12.1666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.8166666666667" style="4" customWidth="1"/>
+    <col min="8" max="8" width="27.8833333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14.9166666666667" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.6666666666667" style="4" customWidth="1"/>
+    <col min="13" max="13" width="18.8166666666667" style="4" customWidth="1"/>
+    <col min="14" max="16370" width="9" style="3"/>
+    <col min="16371" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
-      <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
+      <c r="H1" s="4"/>
       <c r="I1" s="5"/>
       <c r="J1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="5"/>
       <c r="J2" s="4"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>9</v>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:10">
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="8">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>30</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="4">
+      <c r="G6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="6">
         <v>8001</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2">
         <v>2</v>
       </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>30</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="4">
+      <c r="G7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="6">
         <v>8002</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2">
         <v>3</v>
       </c>
-      <c r="F8" s="8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>30</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="G8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="4">
+      <c r="J8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="6">
         <v>8003</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2">
         <v>4</v>
       </c>
-      <c r="F9" s="8">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="G9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="L9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="4">
+      <c r="M9" s="6">
         <v>8004</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>30</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="9" t="s">
+      <c r="G10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="4">
+      <c r="M10" s="6">
         <v>8005</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C11" s="2">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>30</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="9" t="s">
+      <c r="G11" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="4">
+      <c r="M11" s="6">
         <v>8006</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C12" s="2">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2">
         <v>7</v>
       </c>
-      <c r="F12" s="8">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>30</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="4">
+      <c r="G12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="6">
         <v>8007</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2">
         <v>8</v>
       </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>30</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="4">
+      <c r="G13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6">
         <v>8008</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:10">
+    <row r="14" customHeight="1" spans="1:13">
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:10">
+      <c r="F14" s="2"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:10">
+      <c r="F15" s="2"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
+      <c r="F16" s="2"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:13">
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" customHeight="1" spans="3:10">
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" customHeight="1" spans="3:10">
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="3:10">
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" customHeight="1" spans="3:10">
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" customHeight="1" spans="3:10">
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:10">
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:10">
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" customHeight="1" spans="3:10">
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" customHeight="1" spans="3:10">
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="3:10">
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" customHeight="1" spans="3:10">
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:10">
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="3:10">
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="8:9">
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-    </row>
-    <row r="34" customHeight="1" spans="8:9">
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-    </row>
-    <row r="35" customHeight="1" spans="8:9">
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-    </row>
-    <row r="36" customHeight="1" spans="8:9">
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-    </row>
-    <row r="37" customHeight="1" spans="8:9">
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-    </row>
-    <row r="38" customHeight="1" spans="8:9">
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" customHeight="1" spans="8:9">
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="8:9">
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" customHeight="1" spans="8:9">
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-    </row>
-    <row r="42" customHeight="1" spans="8:9">
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-    </row>
-    <row r="43" customHeight="1" spans="8:9">
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" customHeight="1" spans="8:9">
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-    </row>
-    <row r="45" customHeight="1" spans="8:9">
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-    </row>
-    <row r="46" customHeight="1" spans="8:9">
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" customHeight="1" spans="8:9">
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" customHeight="1" spans="8:9">
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="8:9">
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" customHeight="1" spans="8:9">
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="8:9">
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" customHeight="1" spans="8:9">
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-    </row>
-    <row r="54" customHeight="1" spans="8:9">
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-    </row>
-    <row r="55" customHeight="1" spans="8:9">
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-    </row>
-    <row r="56" customHeight="1" spans="8:9">
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" customHeight="1" spans="8:9">
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-    </row>
-    <row r="58" customHeight="1" spans="8:9">
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-    </row>
-    <row r="59" customHeight="1" spans="8:9">
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-    </row>
-    <row r="60" customHeight="1" spans="8:9">
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-    </row>
-    <row r="61" customHeight="1" spans="8:9">
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" customHeight="1" spans="8:9">
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-    </row>
-    <row r="63" customHeight="1" spans="8:9">
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-    </row>
-    <row r="64" customHeight="1" spans="8:9">
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-    </row>
-    <row r="65" customHeight="1" spans="8:9">
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-    </row>
-    <row r="66" customHeight="1" spans="8:9">
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-    </row>
-    <row r="67" customHeight="1" spans="8:9">
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" customHeight="1" spans="8:9">
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-    </row>
-    <row r="69" customHeight="1" spans="8:9">
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" customHeight="1" spans="8:9">
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:13">
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:13">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:13">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:13">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:13">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:13">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:13">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:13">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:13">
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:13">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="3:13">
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:13">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:13">
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:13">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:13">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="7:8">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="7:8">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" customHeight="1" spans="7:8">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" customHeight="1" spans="7:8">
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" customHeight="1" spans="7:8">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="7:8">
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" customHeight="1" spans="7:8">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" customHeight="1" spans="7:8">
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" customHeight="1" spans="7:8">
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" customHeight="1" spans="7:8">
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" customHeight="1" spans="7:8">
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" customHeight="1" spans="7:8">
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" customHeight="1" spans="7:8">
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" customHeight="1" spans="7:8">
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="7:8">
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" customHeight="1" spans="7:8">
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="50" customHeight="1" spans="7:8">
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" customHeight="1" spans="7:8">
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" customHeight="1" spans="7:8">
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="7:8">
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" customHeight="1" spans="7:8">
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" customHeight="1" spans="7:8">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" customHeight="1" spans="7:8">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" customHeight="1" spans="7:8">
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" customHeight="1" spans="7:8">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" customHeight="1" spans="7:8">
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="7:8">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+    </row>
+    <row r="61" customHeight="1" spans="7:8">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+    </row>
+    <row r="62" customHeight="1" spans="7:8">
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+    </row>
+    <row r="63" customHeight="1" spans="7:8">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="7:8">
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="7:8">
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="7:8">
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="7:8">
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="7:8">
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="7:8">
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+    </row>
+    <row r="70" customHeight="1" spans="7:8">
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F3 G3:H3 M3 C4:F4 G4 H4 M4 C5:F5 G5:H5 M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SoulRingConfig.xlsx
+++ b/Excel/SoulRingConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
   <si>
     <t>ID</t>
   </si>
@@ -88,7 +88,7 @@
     <t>1,2,3,1001,1007,27</t>
   </si>
   <si>
-    <t>5000,500,500,5,1,1</t>
+    <t>6000,600,600,5,1,1</t>
   </si>
   <si>
     <t>0,0,0,0,0,0</t>
@@ -109,6 +109,9 @@
     <t>1,2,3,1002,1008,28</t>
   </si>
   <si>
+    <t>8000,800,800,5,1,1</t>
+  </si>
+  <si>
     <t>10002</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>1,2,3,1003,1009,27</t>
   </si>
   <si>
+    <t>10000,1000,1000,5,1,1</t>
+  </si>
+  <si>
     <t>10003</t>
   </si>
   <si>
@@ -127,7 +133,7 @@
     <t>1,2,3,1007,2001,28</t>
   </si>
   <si>
-    <t>10000,1000,1000,5,1,1</t>
+    <t>12000,1200,1200,5,1,1</t>
   </si>
   <si>
     <t>10007</t>
@@ -139,6 +145,9 @@
     <t>1,2,3,1008,2002,27</t>
   </si>
   <si>
+    <t>14000,1400,1400,5,1,1</t>
+  </si>
+  <si>
     <t>10008</t>
   </si>
   <si>
@@ -148,16 +157,19 @@
     <t>1,2,3,1009,2003,28</t>
   </si>
   <si>
+    <t>16000,1600,1600,5,1,1</t>
+  </si>
+  <si>
     <t>10009</t>
   </si>
   <si>
     <t>千万魂环</t>
   </si>
   <si>
-    <t>1,2,3,22,24,27</t>
-  </si>
-  <si>
-    <t>15000,1500,1500,5,5,1</t>
+    <t>1,2,3,22,22,27</t>
+  </si>
+  <si>
+    <t>18000,1800,1800,5,5,1</t>
   </si>
   <si>
     <t>10027</t>
@@ -1369,13 +1381,13 @@
         <v>24</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>21</v>
@@ -1392,22 +1404,22 @@
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2">
         <v>3</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>21</v>
@@ -1424,22 +1436,22 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2">
         <v>4</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>21</v>
@@ -1456,22 +1468,22 @@
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>21</v>
@@ -1488,22 +1500,22 @@
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>21</v>
@@ -1520,22 +1532,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2">
         <v>7</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>21</v>
@@ -1552,22 +1564,22 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2">
         <v>8</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>21</v>
@@ -1679,7 +1691,6 @@
     <row r="23" customHeight="1" spans="3:13">
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
-      <c r="I23" s="5"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
@@ -1758,7 +1769,6 @@
     <row r="32" customHeight="1" spans="3:13">
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="5"/>
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
@@ -1913,7 +1923,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F3 G3:H3 M3 C4:F4 G4 H4 M4 C5:F5 G5:H5 M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SoulRingConfig.xlsx
+++ b/Excel/SoulRingConfig.xlsx
@@ -106,7 +106,7 @@
     <t>百年魂环</t>
   </si>
   <si>
-    <t>1,2,3,1002,1008,28</t>
+    <t>1,2,3,1002,1008,27</t>
   </si>
   <si>
     <t>8000,800,800,5,1,1</t>
@@ -154,7 +154,7 @@
     <t>百万魂环</t>
   </si>
   <si>
-    <t>1,2,3,1009,2003,28</t>
+    <t>1,2,3,1009,2003,27</t>
   </si>
   <si>
     <t>16000,1600,1600,5,1,1</t>

--- a/Excel/SoulRingConfig.xlsx
+++ b/Excel/SoulRingConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -85,10 +85,10 @@
     <t>十年魂环</t>
   </si>
   <si>
-    <t>1,2,3,1001,1007,27</t>
-  </si>
-  <si>
-    <t>6000,600,600,5,1,1</t>
+    <t>1001,1002,1003,2001,1007,27</t>
+  </si>
+  <si>
+    <t>5,5,5,1,1,1</t>
   </si>
   <si>
     <t>0,0,0,0,0,0</t>
@@ -106,10 +106,10 @@
     <t>百年魂环</t>
   </si>
   <si>
-    <t>1,2,3,1002,1008,27</t>
-  </si>
-  <si>
-    <t>8000,800,800,5,1,1</t>
+    <t>1001,1002,1003,2002,1008,27</t>
+  </si>
+  <si>
+    <t>6,6,6,1,1,1</t>
   </si>
   <si>
     <t>10002</t>
@@ -118,10 +118,10 @@
     <t>千年魂环</t>
   </si>
   <si>
-    <t>1,2,3,1003,1009,27</t>
-  </si>
-  <si>
-    <t>10000,1000,1000,5,1,1</t>
+    <t>1001,1002,1003,2003,1009,27</t>
+  </si>
+  <si>
+    <t>7,7,7,1,1,1</t>
   </si>
   <si>
     <t>10003</t>
@@ -130,10 +130,10 @@
     <t>万年魂环</t>
   </si>
   <si>
-    <t>1,2,3,1007,2001,28</t>
-  </si>
-  <si>
-    <t>12000,1200,1200,5,1,1</t>
+    <t>1001,1002,1003,2001,1007,28</t>
+  </si>
+  <si>
+    <t>8,8,8,1,1,1</t>
   </si>
   <si>
     <t>10007</t>
@@ -142,10 +142,7 @@
     <t>十万魂环</t>
   </si>
   <si>
-    <t>1,2,3,1008,2002,27</t>
-  </si>
-  <si>
-    <t>14000,1400,1400,5,1,1</t>
+    <t>9,9,9,1,1,1</t>
   </si>
   <si>
     <t>10008</t>
@@ -154,10 +151,7 @@
     <t>百万魂环</t>
   </si>
   <si>
-    <t>1,2,3,1009,2003,27</t>
-  </si>
-  <si>
-    <t>16000,1600,1600,5,1,1</t>
+    <t>10,10,10,1,1,1</t>
   </si>
   <si>
     <t>10009</t>
@@ -166,10 +160,10 @@
     <t>千万魂环</t>
   </si>
   <si>
-    <t>1,2,3,22,22,27</t>
-  </si>
-  <si>
-    <t>18000,1800,1800,5,5,1</t>
+    <t>1001,1002,1003,22,24,27</t>
+  </si>
+  <si>
+    <t>11,11,11,2,2,1</t>
   </si>
   <si>
     <t>10027</t>
@@ -178,10 +172,10 @@
     <t>亿年魂环</t>
   </si>
   <si>
-    <t>1,2,3,22,24,28</t>
-  </si>
-  <si>
-    <t>20000,2000,2000,5,5,1</t>
+    <t>1001,1002,1003,22,24,28</t>
+  </si>
+  <si>
+    <t>12,12,12,3,3,1</t>
   </si>
   <si>
     <t>10028</t>
@@ -1474,16 +1468,16 @@
         <v>5</v>
       </c>
       <c r="G10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>21</v>
@@ -1500,22 +1494,22 @@
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>21</v>
@@ -1532,22 +1526,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2">
         <v>7</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>21</v>
@@ -1564,22 +1558,22 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2">
         <v>8</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>21</v>
